--- a/data/flo/invoice-numbers.xlsx
+++ b/data/flo/invoice-numbers.xlsx
@@ -392,12 +392,12 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2">
-        <v>1010050331</v>
+        <v>1010050772</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="2">
-        <v>1010050332</v>
+        <v>1010050771</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
